--- a/FLORES DE ESTRADA/Octubre/PRORRATEO Octubre Estrada.xlsx
+++ b/FLORES DE ESTRADA/Octubre/PRORRATEO Octubre Estrada.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\FLORES DE ESTRADA\Septiembre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\FLORES DE ESTRADA\Octubre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ABE1168-0E51-41B6-902E-B3CDD74108EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{779FC210-BEA0-4D0D-908E-127C6BA80493}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="81">
   <si>
     <t>Domicilio:</t>
   </si>
@@ -260,9 +260,6 @@
   </si>
   <si>
     <t>ALCOLEAS, CRISTIAN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ricardo </t>
   </si>
   <si>
     <t>PAWLAK, MARCOS</t>
@@ -285,7 +282,7 @@
     <numFmt numFmtId="164" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -402,6 +399,13 @@
     <font>
       <b/>
       <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -609,7 +613,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
@@ -719,7 +723,6 @@
     <xf numFmtId="44" fontId="9" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="15" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -746,6 +749,8 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="16" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Hipervínculo" xfId="3" builtinId="8"/>
@@ -1105,22 +1110,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="70" t="s">
-        <v>81</v>
-      </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="71"/>
-      <c r="F1" s="71"/>
-      <c r="G1" s="71"/>
-      <c r="H1" s="71"/>
-      <c r="I1" s="71"/>
-      <c r="J1" s="71"/>
-      <c r="K1" s="71"/>
-      <c r="L1" s="71"/>
-      <c r="M1" s="71"/>
-      <c r="N1" s="72"/>
+      <c r="A1" s="69" t="s">
+        <v>80</v>
+      </c>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="70"/>
+      <c r="I1" s="70"/>
+      <c r="J1" s="70"/>
+      <c r="K1" s="70"/>
+      <c r="L1" s="70"/>
+      <c r="M1" s="70"/>
+      <c r="N1" s="71"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="13"/>
@@ -1153,13 +1158,13 @@
       <c r="I4" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="J4" s="68">
+      <c r="J4" s="67">
         <v>1153202676</v>
       </c>
-      <c r="K4" s="68"/>
-      <c r="L4" s="68"/>
-      <c r="M4" s="68"/>
-      <c r="N4" s="69"/>
+      <c r="K4" s="67"/>
+      <c r="L4" s="67"/>
+      <c r="M4" s="67"/>
+      <c r="N4" s="68"/>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
@@ -1285,11 +1290,11 @@
         <v>4.9000000000000004</v>
       </c>
       <c r="F11" s="5">
-        <v>98107.897020000004</v>
-      </c>
-      <c r="G11" s="62">
+        <v>68600.000000000015</v>
+      </c>
+      <c r="G11" s="73">
         <f>F11</f>
-        <v>98107.897020000004</v>
+        <v>68600.000000000015</v>
       </c>
       <c r="H11" s="8">
         <f>F11-G11</f>
@@ -1334,23 +1339,23 @@
         <v>3.89</v>
       </c>
       <c r="F12" s="5">
-        <v>948379.2328399159</v>
+        <v>1086296.6053298286</v>
       </c>
       <c r="G12" s="62"/>
       <c r="H12" s="8">
         <f t="shared" ref="H12:H34" si="0">F12-G12</f>
-        <v>948379.2328399159</v>
+        <v>1086296.6053298286</v>
       </c>
       <c r="I12" s="5">
         <v>0</v>
       </c>
       <c r="J12" s="9">
         <f t="shared" ref="J12:J34" si="1">H12*8.8%</f>
-        <v>83457.37248991261</v>
+        <v>95594.101269024919</v>
       </c>
       <c r="K12" s="44">
         <f>H12+I12+J12</f>
-        <v>1031836.6053298286</v>
+        <v>1181890.7065988535</v>
       </c>
       <c r="L12" s="5">
         <f>C7*E12/100</f>
@@ -1362,7 +1367,7 @@
       </c>
       <c r="N12" s="44">
         <f>K12+L12+M12</f>
-        <v>1086296.6053298286</v>
+        <v>1236350.7065988535</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
@@ -1376,17 +1381,17 @@
         <v>7</v>
       </c>
       <c r="D13" s="55" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E13" s="3">
         <v>4</v>
       </c>
       <c r="F13" s="5">
-        <v>80088.079200000007</v>
-      </c>
-      <c r="G13" s="62">
+        <v>56000</v>
+      </c>
+      <c r="G13" s="73">
         <f>F13</f>
-        <v>80088.079200000007</v>
+        <v>56000</v>
       </c>
       <c r="H13" s="8">
         <f t="shared" si="0"/>
@@ -1415,9 +1420,9 @@
         <f>K13+L13+M13</f>
         <v>56000</v>
       </c>
-      <c r="P13" s="66">
+      <c r="P13" s="65">
         <f>G13+G30</f>
-        <v>103715.06256400001</v>
+        <v>72521</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
@@ -1437,11 +1442,11 @@
         <v>4.9000000000000004</v>
       </c>
       <c r="F14" s="5">
-        <v>98107.897020000004</v>
-      </c>
-      <c r="G14" s="62">
+        <v>68600.000000000015</v>
+      </c>
+      <c r="G14" s="73">
         <f t="shared" ref="G14" si="2">F14</f>
-        <v>98107.897020000004</v>
+        <v>68600.000000000015</v>
       </c>
       <c r="H14" s="8">
         <f t="shared" si="0"/>
@@ -1475,10 +1480,10 @@
       <c r="A15" s="11">
         <v>5</v>
       </c>
-      <c r="B15" s="64" t="s">
+      <c r="B15" s="63" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="65" t="s">
+      <c r="C15" s="64" t="s">
         <v>8</v>
       </c>
       <c r="D15" s="55" t="s">
@@ -1488,11 +1493,11 @@
         <v>3.89</v>
       </c>
       <c r="F15" s="5">
-        <v>77885.657021999999</v>
-      </c>
-      <c r="G15" s="62">
+        <v>54460</v>
+      </c>
+      <c r="G15" s="73">
         <f>F15</f>
-        <v>77885.657021999999</v>
+        <v>54460</v>
       </c>
       <c r="H15" s="8">
         <f t="shared" si="0"/>
@@ -1533,32 +1538,30 @@
       <c r="C16" s="55" t="s">
         <v>9</v>
       </c>
-      <c r="D16" s="55" t="s">
-        <v>78</v>
-      </c>
+      <c r="D16" s="55"/>
       <c r="E16" s="3">
         <v>4</v>
       </c>
       <c r="F16" s="5">
-        <v>110552.1653696</v>
-      </c>
-      <c r="G16" s="62">
-        <v>52088</v>
+        <v>119609.0119221248</v>
+      </c>
+      <c r="G16" s="73">
+        <v>56000</v>
       </c>
       <c r="H16" s="8">
         <f t="shared" si="0"/>
-        <v>58464.165369599999</v>
+        <v>63609.011922124802</v>
       </c>
       <c r="I16" s="5">
         <v>0</v>
       </c>
       <c r="J16" s="9">
         <f t="shared" si="1"/>
-        <v>5144.8465525248002</v>
+        <v>5597.5930491469835</v>
       </c>
       <c r="K16" s="44">
         <f>H16+J16+I16</f>
-        <v>63609.011922124802</v>
+        <v>69206.60497127178</v>
       </c>
       <c r="L16" s="5">
         <f>C7*E16/100</f>
@@ -1570,7 +1573,7 @@
       </c>
       <c r="N16" s="44">
         <f t="shared" si="3"/>
-        <v>119609.0119221248</v>
+        <v>125206.60497127178</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
@@ -1590,11 +1593,11 @@
         <v>4.9000000000000004</v>
       </c>
       <c r="F17" s="5">
-        <v>98107.897020000004</v>
-      </c>
-      <c r="G17" s="62">
+        <v>68600.000000000015</v>
+      </c>
+      <c r="G17" s="73">
         <f t="shared" ref="G17:G21" si="4">F17</f>
-        <v>98107.897020000004</v>
+        <v>68600.000000000015</v>
       </c>
       <c r="H17" s="8">
         <f t="shared" si="0"/>
@@ -1639,11 +1642,11 @@
         <v>3.89</v>
       </c>
       <c r="F18" s="5">
-        <v>77885.657021999999</v>
-      </c>
-      <c r="G18" s="62">
+        <v>54460</v>
+      </c>
+      <c r="G18" s="73">
         <f t="shared" si="4"/>
-        <v>77885.657021999999</v>
+        <v>54460</v>
       </c>
       <c r="H18" s="8">
         <f t="shared" si="0"/>
@@ -1690,11 +1693,11 @@
         <v>4</v>
       </c>
       <c r="F19" s="5">
-        <v>80088.079200000007</v>
-      </c>
-      <c r="G19" s="62">
+        <v>56000</v>
+      </c>
+      <c r="G19" s="73">
         <f t="shared" si="4"/>
-        <v>80088.079200000007</v>
+        <v>56000</v>
       </c>
       <c r="H19" s="8">
         <f t="shared" si="0"/>
@@ -1739,11 +1742,11 @@
         <v>12.66</v>
       </c>
       <c r="F20" s="5">
-        <v>253478.77066800001</v>
-      </c>
-      <c r="G20" s="62">
+        <v>177240</v>
+      </c>
+      <c r="G20" s="73">
         <f>F20</f>
-        <v>253478.77066800001</v>
+        <v>177240</v>
       </c>
       <c r="H20" s="8">
         <f t="shared" si="0"/>
@@ -1790,11 +1793,11 @@
         <v>7.75</v>
       </c>
       <c r="F21" s="5">
-        <v>155170.65345000001</v>
-      </c>
-      <c r="G21" s="63">
+        <v>108500</v>
+      </c>
+      <c r="G21" s="74">
         <f t="shared" si="4"/>
-        <v>155170.65345000001</v>
+        <v>108500</v>
       </c>
       <c r="H21" s="8">
         <f t="shared" si="0"/>
@@ -1832,33 +1835,30 @@
         <v>24</v>
       </c>
       <c r="C22" s="55" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D22" s="55"/>
       <c r="E22" s="1">
         <v>7.51</v>
       </c>
       <c r="F22" s="5">
-        <v>491956.99284546921</v>
-      </c>
-      <c r="G22" s="62">
-        <f>F22</f>
-        <v>491956.99284546921</v>
-      </c>
+        <v>105140</v>
+      </c>
+      <c r="G22" s="62"/>
       <c r="H22" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>105140</v>
       </c>
       <c r="I22" s="5">
         <v>0</v>
       </c>
       <c r="J22" s="9">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>9252.3200000000015</v>
       </c>
       <c r="K22" s="44">
         <f t="shared" ref="K22:K24" si="6">H22+J22+I22</f>
-        <v>0</v>
+        <v>114392.32000000001</v>
       </c>
       <c r="L22" s="5">
         <f>C7*E22/100</f>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="N22" s="44">
         <f t="shared" si="3"/>
-        <v>105140</v>
+        <v>219532.32</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
@@ -1888,25 +1888,23 @@
         <v>4.45</v>
       </c>
       <c r="F23" s="5">
-        <v>551448.40100019309</v>
-      </c>
-      <c r="G23" s="62">
-        <v>326017</v>
-      </c>
+        <v>307569.36428821005</v>
+      </c>
+      <c r="G23" s="62"/>
       <c r="H23" s="8">
         <f t="shared" si="0"/>
-        <v>225431.40100019309</v>
+        <v>307569.36428821005</v>
       </c>
       <c r="I23" s="5">
         <v>0</v>
       </c>
       <c r="J23" s="9">
         <f t="shared" si="1"/>
-        <v>19837.963288016992</v>
+        <v>27066.104057362489</v>
       </c>
       <c r="K23" s="44">
         <f>H23+J23+I23</f>
-        <v>245269.36428821008</v>
+        <v>334635.46834557253</v>
       </c>
       <c r="L23" s="5">
         <f>C7*E23/100</f>
@@ -1918,7 +1916,7 @@
       </c>
       <c r="N23" s="44">
         <f>K23+L23+M23</f>
-        <v>307569.36428821005</v>
+        <v>396935.46834557253</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
@@ -1936,11 +1934,11 @@
         <v>6.17</v>
       </c>
       <c r="F24" s="5">
-        <v>123535.86216600001</v>
-      </c>
-      <c r="G24" s="62">
+        <v>86380</v>
+      </c>
+      <c r="G24" s="73">
         <f>F24</f>
-        <v>123535.86216600001</v>
+        <v>86380</v>
       </c>
       <c r="H24" s="8">
         <f t="shared" si="0"/>
@@ -1987,25 +1985,25 @@
         <v>4.45</v>
       </c>
       <c r="F25" s="5">
-        <v>492365.95434993866</v>
-      </c>
-      <c r="G25" s="62">
-        <v>57949</v>
+        <v>534946.64633273333</v>
+      </c>
+      <c r="G25" s="73">
+        <v>62301</v>
       </c>
       <c r="H25" s="8">
         <f t="shared" si="0"/>
-        <v>434416.95434993866</v>
+        <v>472645.64633273333</v>
       </c>
       <c r="I25" s="5">
         <v>0</v>
       </c>
       <c r="J25" s="9">
         <f t="shared" si="1"/>
-        <v>38228.691982794604</v>
+        <v>41592.816877280537</v>
       </c>
       <c r="K25" s="44">
         <f>H25+J25+I25</f>
-        <v>472645.64633273327</v>
+        <v>514238.46321001387</v>
       </c>
       <c r="L25" s="5">
         <f>C7*E25/100+1</f>
@@ -2017,7 +2015,7 @@
       </c>
       <c r="N25" s="44">
         <f>K25+L25+M25</f>
-        <v>534946.64633273333</v>
+        <v>576539.46321001393</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
@@ -2037,26 +2035,26 @@
         <v>9.19</v>
       </c>
       <c r="F26" s="5">
-        <v>1348192.0105611025</v>
-      </c>
-      <c r="G26" s="62">
-        <f>300000-132973</f>
-        <v>167027</v>
+        <v>1413768.5314904796</v>
+      </c>
+      <c r="G26" s="73">
+        <f>189300-110707</f>
+        <v>78593</v>
       </c>
       <c r="H26" s="8">
         <f t="shared" si="0"/>
-        <v>1181165.0105611025</v>
+        <v>1335175.5314904796</v>
       </c>
       <c r="I26" s="5">
         <v>0</v>
       </c>
       <c r="J26" s="9">
         <f t="shared" si="1"/>
-        <v>103942.52092937703</v>
+        <v>117495.44677116221</v>
       </c>
       <c r="K26" s="44">
         <f>H26+J26+I26</f>
-        <v>1285107.5314904796</v>
+        <v>1452670.9782616417</v>
       </c>
       <c r="L26" s="5">
         <f>C7*E26/100+1</f>
@@ -2068,7 +2066,7 @@
       </c>
       <c r="N26" s="44">
         <f>K26+L26+M26</f>
-        <v>1413768.5314904796</v>
+        <v>1581331.9782616417</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
@@ -2088,11 +2086,11 @@
         <v>1.18</v>
       </c>
       <c r="F27" s="5">
-        <v>23626.983364</v>
-      </c>
-      <c r="G27" s="62">
+        <v>16521</v>
+      </c>
+      <c r="G27" s="73">
         <f>F27</f>
-        <v>23626.983364</v>
+        <v>16521</v>
       </c>
       <c r="H27" s="8">
         <f t="shared" si="0"/>
@@ -2137,23 +2135,23 @@
         <v>1.18</v>
       </c>
       <c r="F28" s="5">
-        <v>129360.94286234761</v>
+        <v>157265.70583423419</v>
       </c>
       <c r="G28" s="62"/>
       <c r="H28" s="8">
         <f t="shared" si="0"/>
-        <v>129360.94286234761</v>
+        <v>157265.70583423419</v>
       </c>
       <c r="I28" s="5">
         <v>0</v>
       </c>
       <c r="J28" s="9">
         <f t="shared" si="1"/>
-        <v>11383.762971886592</v>
+        <v>13839.38211341261</v>
       </c>
       <c r="K28" s="44">
         <f t="shared" si="7"/>
-        <v>140744.70583423419</v>
+        <v>171105.0879476468</v>
       </c>
       <c r="L28" s="5">
         <f>C7*E28/100+1</f>
@@ -2165,7 +2163,7 @@
       </c>
       <c r="N28" s="44">
         <f t="shared" ref="N28:N34" si="8">K28+L28+M28</f>
-        <v>157265.70583423419</v>
+        <v>187626.0879476468</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
@@ -2183,23 +2181,23 @@
         <v>1.18</v>
       </c>
       <c r="F29" s="5">
-        <v>129360.94286234761</v>
+        <v>157265.70583423419</v>
       </c>
       <c r="G29" s="62"/>
       <c r="H29" s="8">
         <f t="shared" si="0"/>
-        <v>129360.94286234761</v>
+        <v>157265.70583423419</v>
       </c>
       <c r="I29" s="5">
         <v>0</v>
       </c>
       <c r="J29" s="9">
         <f t="shared" si="1"/>
-        <v>11383.762971886592</v>
+        <v>13839.38211341261</v>
       </c>
       <c r="K29" s="44">
         <f t="shared" si="7"/>
-        <v>140744.70583423419</v>
+        <v>171105.0879476468</v>
       </c>
       <c r="L29" s="5">
         <f>C7*E29/100+1</f>
@@ -2211,7 +2209,7 @@
       </c>
       <c r="N29" s="44">
         <f t="shared" si="8"/>
-        <v>157265.70583423419</v>
+        <v>187626.0879476468</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
@@ -2229,11 +2227,11 @@
         <v>1.18</v>
       </c>
       <c r="F30" s="5">
-        <v>23626.983364</v>
-      </c>
-      <c r="G30" s="62">
+        <v>16521</v>
+      </c>
+      <c r="G30" s="73">
         <f>F30</f>
-        <v>23626.983364</v>
+        <v>16521</v>
       </c>
       <c r="H30" s="60">
         <f t="shared" si="0"/>
@@ -2278,11 +2276,11 @@
         <v>1.18</v>
       </c>
       <c r="F31" s="5">
-        <v>23626.983364</v>
-      </c>
-      <c r="G31" s="62">
+        <v>16521</v>
+      </c>
+      <c r="G31" s="73">
         <f t="shared" ref="G31:G33" si="9">F31</f>
-        <v>23626.983364</v>
+        <v>16521</v>
       </c>
       <c r="H31" s="8">
         <f t="shared" si="0"/>
@@ -2327,11 +2325,11 @@
         <v>1.18</v>
       </c>
       <c r="F32" s="5">
-        <v>23626.983364</v>
-      </c>
-      <c r="G32" s="62">
+        <v>16521</v>
+      </c>
+      <c r="G32" s="73">
         <f>F32</f>
-        <v>23626.983364</v>
+        <v>16521</v>
       </c>
       <c r="H32" s="8">
         <f t="shared" si="0"/>
@@ -2376,11 +2374,11 @@
         <v>1.18</v>
       </c>
       <c r="F33" s="5">
-        <v>23626.983364</v>
-      </c>
-      <c r="G33" s="62">
+        <v>16521</v>
+      </c>
+      <c r="G33" s="73">
         <f t="shared" si="9"/>
-        <v>23626.983364</v>
+        <v>16521</v>
       </c>
       <c r="H33" s="8">
         <f t="shared" si="0"/>
@@ -2419,33 +2417,30 @@
         <v>41</v>
       </c>
       <c r="C34" s="55" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D34" s="55"/>
       <c r="E34" s="1">
         <v>1.18</v>
       </c>
       <c r="F34" s="5">
-        <v>77301.441059266814</v>
-      </c>
-      <c r="G34" s="62">
-        <f>F34</f>
-        <v>77301.441059266814</v>
-      </c>
+        <v>16521</v>
+      </c>
+      <c r="G34" s="62"/>
       <c r="H34" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>16521</v>
       </c>
       <c r="I34" s="5">
         <v>0</v>
       </c>
       <c r="J34" s="9">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1453.8480000000002</v>
       </c>
       <c r="K34" s="44">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>17974.848000000002</v>
       </c>
       <c r="L34" s="5">
         <f>C7*E34/100+1</f>
@@ -2457,15 +2452,15 @@
       </c>
       <c r="N34" s="44">
         <f t="shared" si="8"/>
-        <v>16521</v>
+        <v>34495.847999999998</v>
       </c>
     </row>
     <row r="35" spans="1:15" s="4" customFormat="1" ht="21" x14ac:dyDescent="0.35">
-      <c r="A35" s="67" t="s">
+      <c r="A35" s="66" t="s">
         <v>42</v>
       </c>
-      <c r="B35" s="67"/>
-      <c r="C35" s="67"/>
+      <c r="B35" s="66"/>
+      <c r="C35" s="66"/>
       <c r="D35" s="52"/>
       <c r="E35" s="45">
         <f>SUM(E11:E34)</f>
@@ -2473,15 +2468,15 @@
       </c>
       <c r="F35" s="46">
         <f>SUM(F11:F34)</f>
-        <v>5539509.4503581822</v>
+        <v>4779827.5710318442</v>
       </c>
       <c r="G35" s="61">
         <f>SUM(G11:G34)</f>
-        <v>2432930.8005127362</v>
+        <v>1078339</v>
       </c>
       <c r="H35" s="47">
         <f>SUM(H11:H34)</f>
-        <v>3106578.6498454455</v>
+        <v>3701488.5710318447</v>
       </c>
       <c r="I35" s="47">
         <f>SUM(I12:I34)</f>
@@ -2489,7 +2484,7 @@
       </c>
       <c r="J35" s="48">
         <f>SUM(J11:J34)</f>
-        <v>273378.92118639924</v>
+        <v>325730.99425080232</v>
       </c>
       <c r="K35" s="48"/>
       <c r="L35" s="47">
@@ -2502,7 +2497,7 @@
       </c>
       <c r="N35" s="56">
         <f>SUM(N11:N34)</f>
-        <v>4779827.5710318442</v>
+        <v>5427089.5652826475</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
@@ -3278,11 +3273,11 @@
       </c>
     </row>
     <row r="29" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A29" s="73" t="s">
+      <c r="A29" s="72" t="s">
         <v>42</v>
       </c>
-      <c r="B29" s="73"/>
-      <c r="C29" s="73"/>
+      <c r="B29" s="72"/>
+      <c r="C29" s="72"/>
       <c r="D29" s="27">
         <f>SUM(D5:D28)</f>
         <v>99.990000000000066</v>

--- a/FLORES DE ESTRADA/Octubre/PRORRATEO Octubre Estrada.xlsx
+++ b/FLORES DE ESTRADA/Octubre/PRORRATEO Octubre Estrada.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\FLORES DE ESTRADA\Octubre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{779FC210-BEA0-4D0D-908E-127C6BA80493}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7154721-6911-4BF3-9027-39BD1AE93122}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -268,7 +268,7 @@
     <t xml:space="preserve">Antonella </t>
   </si>
   <si>
-    <t>EXPENSAS - VENCIMIENTO 15/09  LIQUIDACION : SEPTIEMBRE</t>
+    <t>EXPENSAS - VENCIMIENTO 14/11  LIQUIDACION : OCTUBRE</t>
   </si>
 </sst>
 </file>
@@ -282,7 +282,7 @@
     <numFmt numFmtId="164" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -399,13 +399,6 @@
     <font>
       <b/>
       <sz val="12"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -613,7 +606,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
@@ -749,8 +742,7 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Hipervínculo" xfId="3" builtinId="8"/>
@@ -1292,7 +1284,7 @@
       <c r="F11" s="5">
         <v>68600.000000000015</v>
       </c>
-      <c r="G11" s="73">
+      <c r="G11" s="62">
         <f>F11</f>
         <v>68600.000000000015</v>
       </c>
@@ -1389,7 +1381,7 @@
       <c r="F13" s="5">
         <v>56000</v>
       </c>
-      <c r="G13" s="73">
+      <c r="G13" s="62">
         <f>F13</f>
         <v>56000</v>
       </c>
@@ -1444,7 +1436,7 @@
       <c r="F14" s="5">
         <v>68600.000000000015</v>
       </c>
-      <c r="G14" s="73">
+      <c r="G14" s="62">
         <f t="shared" ref="G14" si="2">F14</f>
         <v>68600.000000000015</v>
       </c>
@@ -1495,7 +1487,7 @@
       <c r="F15" s="5">
         <v>54460</v>
       </c>
-      <c r="G15" s="73">
+      <c r="G15" s="62">
         <f>F15</f>
         <v>54460</v>
       </c>
@@ -1545,7 +1537,7 @@
       <c r="F16" s="5">
         <v>119609.0119221248</v>
       </c>
-      <c r="G16" s="73">
+      <c r="G16" s="62">
         <v>56000</v>
       </c>
       <c r="H16" s="8">
@@ -1595,7 +1587,7 @@
       <c r="F17" s="5">
         <v>68600.000000000015</v>
       </c>
-      <c r="G17" s="73">
+      <c r="G17" s="62">
         <f t="shared" ref="G17:G21" si="4">F17</f>
         <v>68600.000000000015</v>
       </c>
@@ -1644,7 +1636,7 @@
       <c r="F18" s="5">
         <v>54460</v>
       </c>
-      <c r="G18" s="73">
+      <c r="G18" s="62">
         <f t="shared" si="4"/>
         <v>54460</v>
       </c>
@@ -1695,7 +1687,7 @@
       <c r="F19" s="5">
         <v>56000</v>
       </c>
-      <c r="G19" s="73">
+      <c r="G19" s="62">
         <f t="shared" si="4"/>
         <v>56000</v>
       </c>
@@ -1744,7 +1736,7 @@
       <c r="F20" s="5">
         <v>177240</v>
       </c>
-      <c r="G20" s="73">
+      <c r="G20" s="62">
         <f>F20</f>
         <v>177240</v>
       </c>
@@ -1795,7 +1787,7 @@
       <c r="F21" s="5">
         <v>108500</v>
       </c>
-      <c r="G21" s="74">
+      <c r="G21" s="73">
         <f t="shared" si="4"/>
         <v>108500</v>
       </c>
@@ -1936,7 +1928,7 @@
       <c r="F24" s="5">
         <v>86380</v>
       </c>
-      <c r="G24" s="73">
+      <c r="G24" s="62">
         <f>F24</f>
         <v>86380</v>
       </c>
@@ -1987,7 +1979,7 @@
       <c r="F25" s="5">
         <v>534946.64633273333</v>
       </c>
-      <c r="G25" s="73">
+      <c r="G25" s="62">
         <v>62301</v>
       </c>
       <c r="H25" s="8">
@@ -2037,7 +2029,7 @@
       <c r="F26" s="5">
         <v>1413768.5314904796</v>
       </c>
-      <c r="G26" s="73">
+      <c r="G26" s="62">
         <f>189300-110707</f>
         <v>78593</v>
       </c>
@@ -2088,7 +2080,7 @@
       <c r="F27" s="5">
         <v>16521</v>
       </c>
-      <c r="G27" s="73">
+      <c r="G27" s="62">
         <f>F27</f>
         <v>16521</v>
       </c>
@@ -2229,7 +2221,7 @@
       <c r="F30" s="5">
         <v>16521</v>
       </c>
-      <c r="G30" s="73">
+      <c r="G30" s="62">
         <f>F30</f>
         <v>16521</v>
       </c>
@@ -2278,7 +2270,7 @@
       <c r="F31" s="5">
         <v>16521</v>
       </c>
-      <c r="G31" s="73">
+      <c r="G31" s="62">
         <f t="shared" ref="G31:G33" si="9">F31</f>
         <v>16521</v>
       </c>
@@ -2327,7 +2319,7 @@
       <c r="F32" s="5">
         <v>16521</v>
       </c>
-      <c r="G32" s="73">
+      <c r="G32" s="62">
         <f>F32</f>
         <v>16521</v>
       </c>
@@ -2376,7 +2368,7 @@
       <c r="F33" s="5">
         <v>16521</v>
       </c>
-      <c r="G33" s="73">
+      <c r="G33" s="62">
         <f t="shared" si="9"/>
         <v>16521</v>
       </c>
